--- a/回後買上漲圖表(基礎版)_20260616/回後買上漲基礎版_20260616.xlsx
+++ b/回後買上漲圖表(基礎版)_20260616/回後買上漲基礎版_20260616.xlsx
@@ -487,11 +487,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -551,31 +551,31 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>7777.TWO</t>
+          <t>3311.TW</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>能率亞洲</t>
+          <t>閎暉</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>43.25</v>
+        <v>41.3</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>41.6</v>
+        <v>38.15</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>13158</v>
+        <v>3897</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>5188</v>
+        <v>1701</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>38.3</v>
+        <v>36.54</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -586,31 +586,31 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>6179.TWO</t>
+          <t>3041.TW</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>亞通</t>
+          <t>揚智</t>
         </is>
       </c>
       <c r="C3" s="8" t="n">
-        <v>25.3</v>
+        <v>27</v>
       </c>
       <c r="D3" s="8" t="n">
-        <v>24.25</v>
+        <v>25.55</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>4043</v>
+        <v>5593</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>1797</v>
+        <v>2582</v>
       </c>
       <c r="G3" s="10" t="n">
         <v>2.2</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>24.17</v>
+        <v>25.15</v>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
@@ -621,31 +621,31 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>1905.TW</t>
+          <t>5392.TWO</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>華紙</t>
+          <t>能率</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>14.15</v>
+        <v>44.9</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.15</v>
+        <v>43.8</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>14948</v>
+        <v>6933</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>7057</v>
+        <v>3291</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>2.1</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>12.56</v>
+        <v>43.81</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
@@ -656,31 +656,31 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>1907.TW</t>
+          <t>4952.TW</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>永豐餘</t>
+          <t>凌通</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>26.95</v>
+        <v>58.5</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>26.45</v>
+        <v>56.6</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>3470</v>
+        <v>4808</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>1739</v>
+        <v>2356</v>
       </c>
       <c r="G5" s="10" t="n">
         <v>2</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>25.16</v>
+        <v>51.86</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
@@ -691,31 +691,31 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2633.TW</t>
+          <t>8215.TW</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>台灣高鐵</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>26.15</v>
+        <v>30.55</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>25.7</v>
+        <v>29.85</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>17800</v>
+        <v>8931</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9048</v>
+        <v>4609</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>25.44</v>
+        <v>29.35</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
@@ -726,31 +726,31 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>2399.TW</t>
+          <t>6220.TWO</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>映泰</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>52.8</v>
+        <v>37</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>48.8</v>
+        <v>35.45</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>14011</v>
+        <v>2673</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>7987</v>
+        <v>1403</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>47.7</v>
+        <v>33.08</v>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
@@ -761,31 +761,31 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2867.TW</t>
+          <t>3035.TW</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>三商壽</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>8.529999999999999</v>
+        <v>200.2</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>8.48</v>
+        <v>189.3</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>37888</v>
+        <v>13334</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>22804</v>
+        <v>6930</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>7.9</v>
+        <v>195.69</v>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
@@ -796,31 +796,31 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>8074.TWO</t>
+          <t>2375.TW</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>凱美</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>77</v>
+        <v>189.5</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>74.2</v>
+        <v>177</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>4852</v>
+        <v>13207</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>3016</v>
+        <v>7914</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>74.48</v>
+        <v>149.82</v>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
@@ -831,31 +831,31 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>3003.TW</t>
+          <t>6668.TW</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>健和興</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>67.40000000000001</v>
+        <v>39.85</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>65.5</v>
+        <v>39.05</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4806</v>
+        <v>1750</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3118</v>
+        <v>1028</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>62.8</v>
+        <v>39</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
@@ -866,31 +866,31 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>5880.TW</t>
+          <t>3321.TW</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>同泰</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>24.6</v>
+        <v>22.45</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>24.35</v>
+        <v>20.95</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>41277</v>
+        <v>1812</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>27305</v>
+        <v>1152</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>23.28</v>
+        <v>18.94</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>6742.TW</t>
+          <t>3717.TW</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>聯嘉投控</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>61.4</v>
+        <v>22.25</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>57.3</v>
+        <v>20.65</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6835</v>
+        <v>3460</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4558</v>
+        <v>2128</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>58.41</v>
+        <v>22.14</v>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
@@ -936,31 +936,31 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>2882.TW</t>
+          <t>3294.TWO</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>英濟</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>109.5</v>
+        <v>39.4</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>105.5</v>
+        <v>36.8</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>54267</v>
+        <v>2377</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>37840</v>
+        <v>1455</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>91.69</v>
+        <v>39.35</v>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
@@ -971,31 +971,31 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>6180.TWO</t>
+          <t>4958.TW</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>橘子</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>48.3</v>
+        <v>590</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>44.6</v>
+        <v>578</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3389</v>
+        <v>49593</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2641</v>
+        <v>33034</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>42.5</v>
+        <v>509.6</v>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
@@ -1006,31 +1006,31 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>4904.TW</t>
+          <t>8936.TWO</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>國統</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>112.5</v>
+        <v>57.9</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>112</v>
+        <v>57.7</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>13212</v>
+        <v>14121</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>10046</v>
+        <v>9851</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>100.58</v>
+        <v>53.81</v>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
@@ -1041,31 +1041,31 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>1409.TW</t>
+          <t>6719.TW</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>26.9</v>
+        <v>240.5</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>26.5</v>
+        <v>224.5</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>15308</v>
+        <v>1447</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>12176</v>
+        <v>1096</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>1.3</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>23.12</v>
+        <v>235.82</v>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
@@ -1076,31 +1076,31 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>2884.TW</t>
+          <t>3019.TW</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>亞光</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>35.2</v>
+        <v>158</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>34.85</v>
+        <v>151.5</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>59482</v>
+        <v>16499</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>50935</v>
+        <v>12970</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>32.58</v>
+        <v>151.18</v>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
@@ -1111,31 +1111,31 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>1312.TW</t>
+          <t>3260.TWO</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>國喬</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>13.15</v>
+        <v>423</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>13.1</v>
+        <v>422</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>13800</v>
+        <v>16126</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>11099</v>
+        <v>12817</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.24</v>
+        <v>417.52</v>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
@@ -1146,31 +1146,31 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>2455.TW</t>
+          <t>4721.TWO</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>美琪瑪</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>405.5</v>
+        <v>101</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>373.5</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>17707</v>
+        <v>4601</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>14601</v>
+        <v>3409</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>394.88</v>
+        <v>90.42</v>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
@@ -1181,31 +1181,31 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2892.TW</t>
+          <t>3707.TWO</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>漢磊</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>31.8</v>
+        <v>81.7</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>31.65</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>50724</v>
+        <v>14741</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>50490</v>
+        <v>11077</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>28.96</v>
+        <v>79.87</v>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
@@ -1216,31 +1216,31 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>2412.TW</t>
+          <t>6187.TWO</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>146.5</v>
+        <v>1130</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>146</v>
+        <v>1110</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>12835</v>
+        <v>3006</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>12603</v>
+        <v>2508</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>140.45</v>
+        <v>1109.25</v>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
@@ -1251,31 +1251,31 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>8926.TW</t>
+          <t>2465.TW</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>麗臺</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>76.8</v>
+        <v>83</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>75</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>14307</v>
+        <v>2301</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>15456</v>
+        <v>1899</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>69.03</v>
+        <v>82.28</v>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
@@ -1286,31 +1286,31 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>2379.TW</t>
+          <t>3596.TW</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>678</v>
+        <v>190.5</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>644</v>
+        <v>186.5</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>4254</v>
+        <v>1901</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>4960</v>
+        <v>1608</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>616.2</v>
+        <v>186.65</v>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
@@ -1321,31 +1321,31 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2345.TW</t>
+          <t>6259.TWO</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2520</v>
+        <v>30.35</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>2475</v>
+        <v>29.65</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3068</v>
+        <v>2906</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3247</v>
+        <v>2339</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>2464.5</v>
+        <v>26.54</v>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
@@ -1356,31 +1356,31 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>9940.TW</t>
+          <t>1563.TW</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>信義</t>
+          <t>巧新</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>20.25</v>
+        <v>64</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>19.9</v>
+        <v>61.7</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>963</v>
+        <v>1142</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>1205</v>
+        <v>1079</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>18.73</v>
+        <v>58.29</v>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
@@ -1391,31 +1391,31 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2347.TW</t>
+          <t>2316.TW</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>楠梓電</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>93</v>
+        <v>171.5</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>91.40000000000001</v>
+        <v>162</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>7038</v>
+        <v>5586</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>9927</v>
+        <v>5093</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>87.88</v>
+        <v>160.98</v>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
@@ -1426,31 +1426,31 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>6446.TW</t>
+          <t>9933.TW</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>中鼎</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>991</v>
+        <v>42.8</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>976</v>
+        <v>42.1</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>1994</v>
+        <v>7999</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>2961</v>
+        <v>6967</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>907.5</v>
+        <v>40.42</v>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
@@ -1461,31 +1461,31 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>3550.TW</t>
+          <t>2337.TW</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>聯穎</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>30.85</v>
+        <v>159</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>30.4</v>
+        <v>148</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>10936</v>
+        <v>26842</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>14772</v>
+        <v>23986</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>23.6</v>
+        <v>152.57</v>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
@@ -1496,31 +1496,31 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>3290.TWO</t>
+          <t>3234.TWO</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>東浦</t>
+          <t>光環</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>66</v>
+        <v>122.5</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>64.2</v>
+        <v>116</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>3939</v>
+        <v>2782</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>5513</v>
+        <v>2600</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>52.12</v>
+        <v>113.82</v>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
@@ -1531,31 +1531,31 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>3293.TWO</t>
+          <t>6166.TW</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>772</v>
+        <v>141</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>761</v>
+        <v>134.5</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1697</v>
+        <v>3624</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3110</v>
+        <v>3780</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>765.85</v>
+        <v>128.6</v>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
@@ -1566,31 +1566,31 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>3147.TWO</t>
+          <t>3504.TW</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>揚明光</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>350</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>344.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>527</v>
+        <v>2302</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>1085</v>
+        <v>2378</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>246.55</v>
+        <v>79.64</v>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
@@ -1601,33 +1601,1503 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2348.TW</t>
+          <t>3049.TW</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>海悅</t>
+          <t>精金</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>14.75</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>73.5</v>
+        <v>14.5</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1223</v>
+        <v>11296</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2808</v>
+        <v>11469</v>
       </c>
       <c r="G32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>0052.TW</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>富邦科技</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>60.25</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>30851</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>30763</v>
+      </c>
+      <c r="G33" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>59.59</v>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>8110.TW</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>華東</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>11273</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>11799</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>55.48</v>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>2646.TW</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>星宇航空</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>5954</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>5895</v>
+      </c>
+      <c r="G35" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>4973.TWO</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>廣穎</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>199</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>3093</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>3119</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>154.6</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>3044.TW</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>520</v>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>509</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>3334</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>3911</v>
+      </c>
+      <c r="G37" s="10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>497.5</v>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>6788.TWO</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>華景電</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>449</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>1965</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>2152</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>414.28</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>3008.TW</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="n">
+        <v>4420</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>4355</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>3302</v>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>3619</v>
+      </c>
+      <c r="G39" s="10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>3742.5</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2303.TW</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>141.5</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>137.5</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>325943</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>352781</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>128.9</v>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>4760.TWO</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>勤凱</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="n">
+        <v>401.5</v>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>389</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>1546</v>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>1752</v>
+      </c>
+      <c r="G41" s="10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>383.18</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>3704.TW</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>合勤控</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>4329</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>5080</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>45.34</v>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>6548.TWO</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>長科*</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>2801</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>3510</v>
+      </c>
+      <c r="G43" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>72.95</v>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>5426.TWO</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>振發</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>2980</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>3885</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>3114.TWO</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>好德</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="n">
+        <v>43.45</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>41.95</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>952</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>1210</v>
+      </c>
+      <c r="G45" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H45" s="8" t="n">
+        <v>34.79</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2329.TW</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>華泰</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>6392</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>7990</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>55.11</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>0055.TW</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>元大MSCI金融</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="n">
+        <v>41</v>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>40.57</v>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>941</v>
+      </c>
+      <c r="F47" s="9" t="n">
+        <v>1185</v>
+      </c>
+      <c r="G47" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H47" s="8" t="n">
+        <v>36.82</v>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>3093.TWO</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>港建*</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>3440</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>4542</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>56.53</v>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>8358.TWO</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>金居</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="n">
+        <v>624</v>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>584</v>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>1758</v>
+      </c>
+      <c r="F49" s="9" t="n">
+        <v>2121</v>
+      </c>
+      <c r="G49" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>563.4</v>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>5289.TWO</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>宜鼎</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>1920</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>1830</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>3524</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>4556</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>1789.25</v>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>2330.TW</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="n">
+        <v>2375</v>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>2325</v>
+      </c>
+      <c r="E51" s="9" t="n">
+        <v>25573</v>
+      </c>
+      <c r="F51" s="9" t="n">
+        <v>31557</v>
+      </c>
+      <c r="G51" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H51" s="8" t="n">
+        <v>2300.04</v>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2454.TW</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>4470</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>4415</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>10400</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>12447</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>4172.75</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>2405.TW</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>輔信</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="D53" s="8" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="E53" s="9" t="n">
+        <v>4275</v>
+      </c>
+      <c r="F53" s="9" t="n">
+        <v>5584</v>
+      </c>
+      <c r="G53" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H53" s="8" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>3481.TW</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>群創</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>98818</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>123286</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>47.66</v>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>3037.TW</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="n">
+        <v>960</v>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>930</v>
+      </c>
+      <c r="E55" s="9" t="n">
+        <v>15473</v>
+      </c>
+      <c r="F55" s="9" t="n">
+        <v>20619</v>
+      </c>
+      <c r="G55" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H55" s="8" t="n">
+        <v>958</v>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2428.TW</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>興勤</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>310</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>302</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>3268</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>4064</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>268.35</v>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>3149.TW</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>正達</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="E57" s="9" t="n">
+        <v>4095</v>
+      </c>
+      <c r="F57" s="9" t="n">
+        <v>5102</v>
+      </c>
+      <c r="G57" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H57" s="8" t="n">
+        <v>75.51000000000001</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>0050.TW</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>元大台灣50</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>95906</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>134795</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>101.44</v>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>3653.TW</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="n">
+        <v>3835</v>
+      </c>
+      <c r="D59" s="8" t="n">
+        <v>3820</v>
+      </c>
+      <c r="E59" s="9" t="n">
+        <v>1307</v>
+      </c>
+      <c r="F59" s="9" t="n">
+        <v>1907</v>
+      </c>
+      <c r="G59" s="10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H59" s="8" t="n">
+        <v>3652.5</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>4976.TW</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>佳凌</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>2908</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>3885</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>32.71</v>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>3362.TWO</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>先進光</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>175.5</v>
+      </c>
+      <c r="E61" s="9" t="n">
+        <v>6849</v>
+      </c>
+      <c r="F61" s="9" t="n">
+        <v>9379</v>
+      </c>
+      <c r="G61" s="10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H61" s="8" t="n">
+        <v>133.52</v>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>6862.TW</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>三集瑞-KY</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>201</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>1755</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>2519</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>192.45</v>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>3357.TWO</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>臺慶科</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="n">
+        <v>322</v>
+      </c>
+      <c r="D63" s="8" t="n">
+        <v>307.5</v>
+      </c>
+      <c r="E63" s="9" t="n">
+        <v>13925</v>
+      </c>
+      <c r="F63" s="9" t="n">
+        <v>19862</v>
+      </c>
+      <c r="G63" s="10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H63" s="8" t="n">
+        <v>278.7</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>4931.TWO</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>新盛力</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>252</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>249.5</v>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>10267</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>16327</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>230.38</v>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>1319.TW</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>東陽</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="n">
+        <v>105</v>
+      </c>
+      <c r="D65" s="8" t="n">
+        <v>103</v>
+      </c>
+      <c r="E65" s="9" t="n">
+        <v>5332</v>
+      </c>
+      <c r="F65" s="9" t="n">
+        <v>8237</v>
+      </c>
+      <c r="G65" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H65" s="8" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>6155.TW</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>鈞寶</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>18659</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>31391</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>69.63</v>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>3443.TW</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="n">
+        <v>4815</v>
+      </c>
+      <c r="D67" s="8" t="n">
+        <v>4455</v>
+      </c>
+      <c r="E67" s="9" t="n">
+        <v>1033</v>
+      </c>
+      <c r="F67" s="9" t="n">
+        <v>1863</v>
+      </c>
+      <c r="G67" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H67" s="8" t="n">
+        <v>4621.09</v>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>4919.TW</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>新唐</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>193</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>188</v>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>7773</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>13711</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>187.08</v>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>3450.TW</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>聯鈞</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="n">
+        <v>507</v>
+      </c>
+      <c r="D69" s="8" t="n">
+        <v>482</v>
+      </c>
+      <c r="E69" s="9" t="n">
+        <v>5283</v>
+      </c>
+      <c r="F69" s="9" t="n">
+        <v>9626</v>
+      </c>
+      <c r="G69" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H69" s="8" t="n">
+        <v>486.28</v>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2327.TW</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>919</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>39733</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>76019</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H70" s="3" t="n">
+        <v>732.98</v>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>3023.TW</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>信邦</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="n">
+        <v>319</v>
+      </c>
+      <c r="D71" s="8" t="n">
+        <v>317</v>
+      </c>
+      <c r="E71" s="9" t="n">
+        <v>948</v>
+      </c>
+      <c r="F71" s="9" t="n">
+        <v>1785</v>
+      </c>
+      <c r="G71" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H71" s="8" t="n">
+        <v>314.42</v>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>1809.TW</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>中釉</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>6617</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>14728</v>
+      </c>
+      <c r="G72" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="H32" s="3" t="n">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
+      <c r="H72" s="3" t="n">
+        <v>48.27</v>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>6207.TWO</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>雷科</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="n">
+        <v>136</v>
+      </c>
+      <c r="D73" s="8" t="n">
+        <v>134</v>
+      </c>
+      <c r="E73" s="9" t="n">
+        <v>7493</v>
+      </c>
+      <c r="F73" s="9" t="n">
+        <v>16740</v>
+      </c>
+      <c r="G73" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H73" s="8" t="n">
+        <v>116.48</v>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>8996.TW</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>1255</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>1225</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>1386</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>4060</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>1139.2</v>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
         <is>
           <t>點我查看</t>
         </is>
@@ -1666,6 +3136,48 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId73"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
